--- a/Veenkampen/misc/BADM-Instrument_Ops/VK-BADM-Instrument_Ops.xlsx
+++ b/Veenkampen/misc/BADM-Instrument_Ops/VK-BADM-Instrument_Ops.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\ESG\DOW_MAQ\MAQ_Archive\Veenkampen_archive\FLUXNET\Veenkampen\misc\BADM-Instrument_Ops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5107BB0B-1A37-488E-9AAA-1073545B6918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F5DF23-D4FE-4049-986A-573891CBE370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="-6525" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrument_Ops" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="494">
   <si>
     <t>Variable</t>
   </si>
@@ -1290,57 +1290,9 @@
     <t>sjoerd.barten@wur.nl</t>
   </si>
   <si>
-    <t>TAU_1_1_1;TAU_SSITC_TEST_1_1_1;H_1_1_1;H_SSITC_TEST_1_1_1;LE_1_1_1;LE_SSITC_TEST_1_1_1;FC_1_1_1;FC_SSITC_TEST_1_1_1;FH2O_1_1_1;SH_1_1_1;SLE_1_1_1;SC_1_1_1;CO2_1_1_1;H2O_1_1_1;T_SONIC_1_1_1;TA_1_1_1;PA_1_1_1;RH_1_1_1;VPD_PI_1_1_1;T_DP_1_1_1;WS_1_1_1;WS_MAX_1_1_1;WD_1_1_1;USTAR_1_1_1;MO_LENGTH_1_1_1;ZL_1_1_1;FETCH_70_1_1_1;FETCH_90_1_1_1</t>
-  </si>
-  <si>
-    <t>TA_3_1_1;TA_2_1_1;TA_2_2_1;TA_2_1_2;</t>
-  </si>
-  <si>
-    <t>RH_2_1_1;</t>
-  </si>
-  <si>
-    <t>SW_IN_1_1_1;SW_OUT_1_1_1;SW_DIF_1_1_1;</t>
-  </si>
-  <si>
-    <t>LW_IN_1_1_1;LW_OUT_1_1_1;</t>
-  </si>
-  <si>
-    <t>P_1_1_1;</t>
-  </si>
-  <si>
-    <t>PA_2_1_1;</t>
-  </si>
-  <si>
-    <t>WS_3_1_1;WS_MAX_3_1_1;</t>
-  </si>
-  <si>
-    <t>WS_2_1_1;WS_MAX_2_1_1;WD_2_1_1;WS_2_2_1;WS_MAX_2_2_1;WD_2_2_1;</t>
-  </si>
-  <si>
-    <t>WTD_1_1_1;</t>
-  </si>
-  <si>
-    <t>TS_1_1_1;TS_1_2_1;TS_1_3_1;TS_1_4_1;TS_1_5_1;TS_1_6_1;TS_2_1_1;TS_2_2_1;TS_2_3_1;TS_2_4_1;</t>
-  </si>
-  <si>
-    <t>G_1_1_1;G_2_1_1;G_3_1_1;G_4_1_1;</t>
-  </si>
-  <si>
-    <t>SWC_1_1_1;SWC_1_2_1;SWC_1_3_1;SWC_1_4_1;SWC_2_1_1;SWC_2_2_1;SWC_2_3_1;SWC_2_4_1;SWC_3_1_1;</t>
-  </si>
-  <si>
-    <t>10 (2_1_x); 2 (2_2_x)</t>
-  </si>
-  <si>
-    <t>-0.05;-0.10;-0.20;-0.50;-1.00;-1.50;-0.05;-0.10;-0.20;-0.50</t>
-  </si>
-  <si>
     <t>-0.06</t>
   </si>
   <si>
-    <t>-0.065;-0.125;-0.250;-0.500;-0.065;-0.125;-0.250;-0.500;-0.065;</t>
-  </si>
-  <si>
     <t>VK_TEMP_1</t>
   </si>
   <si>
@@ -1378,6 +1330,189 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>201401010000</t>
+  </si>
+  <si>
+    <t>TA_3_1_1</t>
+  </si>
+  <si>
+    <t>TA_2_1_1</t>
+  </si>
+  <si>
+    <t>TA_2_2_1</t>
+  </si>
+  <si>
+    <t>TA_2_1_2</t>
+  </si>
+  <si>
+    <t>RH_2_1_1</t>
+  </si>
+  <si>
+    <t>SW_IN_1_1_1</t>
+  </si>
+  <si>
+    <t>SW_OUT_1_1_1</t>
+  </si>
+  <si>
+    <t>LW_IN_1_1_1</t>
+  </si>
+  <si>
+    <t>LW_OUT_1_1_1</t>
+  </si>
+  <si>
+    <t>SW_DIF_1_1_1</t>
+  </si>
+  <si>
+    <t>P_1_1_1</t>
+  </si>
+  <si>
+    <t>PA_2_1_1</t>
+  </si>
+  <si>
+    <t>WS_MAX_3_1_1</t>
+  </si>
+  <si>
+    <t>WS_3_1_1</t>
+  </si>
+  <si>
+    <t>WS_2_1_1</t>
+  </si>
+  <si>
+    <t>WS_MAX_2_1_1</t>
+  </si>
+  <si>
+    <t>WD_2_1_1</t>
+  </si>
+  <si>
+    <t>WS_2_2_1</t>
+  </si>
+  <si>
+    <t>WS_MAX_2_2_1</t>
+  </si>
+  <si>
+    <t>WD_2_2_1</t>
+  </si>
+  <si>
+    <t>WTD_1_1_1</t>
+  </si>
+  <si>
+    <t>G_1_1_1</t>
+  </si>
+  <si>
+    <t>G_2_1_1</t>
+  </si>
+  <si>
+    <t>G_3_1_1</t>
+  </si>
+  <si>
+    <t>G_4_1_1</t>
+  </si>
+  <si>
+    <t>SWC_1_1_1</t>
+  </si>
+  <si>
+    <t>-0.065</t>
+  </si>
+  <si>
+    <t>-0.125</t>
+  </si>
+  <si>
+    <t>SWC_1_2_1</t>
+  </si>
+  <si>
+    <t>SWC_1_3_1</t>
+  </si>
+  <si>
+    <t>-0.250</t>
+  </si>
+  <si>
+    <t>SWC_1_4_1</t>
+  </si>
+  <si>
+    <t>-0.500</t>
+  </si>
+  <si>
+    <t>SWC_2_1_1</t>
+  </si>
+  <si>
+    <t>SWC_2_2_1</t>
+  </si>
+  <si>
+    <t>SWC_2_3_1</t>
+  </si>
+  <si>
+    <t>SWC_2_4_1</t>
+  </si>
+  <si>
+    <t>SWC_3_1_1</t>
+  </si>
+  <si>
+    <t>TS_1_1_1</t>
+  </si>
+  <si>
+    <t>-0.05</t>
+  </si>
+  <si>
+    <t>-0.10</t>
+  </si>
+  <si>
+    <t>TS_1_3_1</t>
+  </si>
+  <si>
+    <t>-0.20</t>
+  </si>
+  <si>
+    <t>TS_1_4_1</t>
+  </si>
+  <si>
+    <t>-0.50</t>
+  </si>
+  <si>
+    <t>TS_1_5_1</t>
+  </si>
+  <si>
+    <t>-1.00</t>
+  </si>
+  <si>
+    <t>TS_1_6_1</t>
+  </si>
+  <si>
+    <t>-1.50</t>
+  </si>
+  <si>
+    <t>TS_2_1_1</t>
+  </si>
+  <si>
+    <t>TS_2_2_1</t>
+  </si>
+  <si>
+    <t>TS_2_3_1</t>
+  </si>
+  <si>
+    <t>TS_2_4_1</t>
+  </si>
+  <si>
+    <t>TS_1_2_1</t>
+  </si>
+  <si>
+    <t>TA_1_1_1</t>
+  </si>
+  <si>
+    <t>PA_1_1_1</t>
+  </si>
+  <si>
+    <t>RH_1_1_1</t>
+  </si>
+  <si>
+    <t>WS_1_1_1</t>
+  </si>
+  <si>
+    <t>WS_MAX_1_1_1</t>
+  </si>
+  <si>
+    <t>WD_1_1_1</t>
   </si>
 </sst>
 </file>
@@ -1421,7 +1556,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1476,8 +1611,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1500,12 +1641,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1514,10 +1670,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1540,18 +1692,24 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1834,573 +1992,1530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:BB23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="91" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="19.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="41" width="14" bestFit="1" customWidth="1"/>
+    <col min="42" max="54" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="120" width="45.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16"/>
-    </row>
-    <row r="2" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+    </row>
+    <row r="2" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="E2" s="17"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="14" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="16">
         <v>20250521</v>
       </c>
-      <c r="E6" s="20"/>
-    </row>
-    <row r="7" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="F7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="K7" t="s">
         <v>253</v>
       </c>
-      <c r="G7" t="s">
+      <c r="L7" t="s">
+        <v>253</v>
+      </c>
+      <c r="M7" t="s">
+        <v>253</v>
+      </c>
+      <c r="N7" t="s">
+        <v>253</v>
+      </c>
+      <c r="O7" t="s">
         <v>237</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="P7" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="Q7" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="S7" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="T7" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="U7" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="K7" t="s">
+      <c r="V7" t="s">
         <v>227</v>
       </c>
-      <c r="L7" t="s">
+      <c r="W7" t="s">
         <v>213</v>
       </c>
-      <c r="M7" t="s">
+      <c r="X7" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y7" t="s">
         <v>217</v>
       </c>
-      <c r="N7" s="15" t="s">
+      <c r="Z7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE7" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="AF7" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="AG7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AI7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AJ7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AK7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AL7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AM7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AN7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AO7" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="AP7" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="AQ7" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="AR7" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="AS7" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="AT7" s="12" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="AU7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AV7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AW7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AX7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AY7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="AZ7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="BA7" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="BB7" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="14">
+        <v>30</v>
+      </c>
+      <c r="E8" s="14">
         <v>258</v>
       </c>
-      <c r="E8">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>436</v>
-      </c>
-      <c r="G8" t="s">
-        <v>437</v>
-      </c>
-      <c r="H8" t="s">
-        <v>438</v>
-      </c>
-      <c r="I8" t="s">
-        <v>439</v>
-      </c>
-      <c r="J8" t="s">
-        <v>440</v>
+      <c r="F8" s="14">
+        <v>258</v>
+      </c>
+      <c r="G8" s="14">
+        <v>258</v>
+      </c>
+      <c r="H8" s="14">
+        <v>258</v>
+      </c>
+      <c r="I8" s="14">
+        <v>258</v>
+      </c>
+      <c r="J8" s="14">
+        <v>258</v>
       </c>
       <c r="K8" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="L8" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="M8" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="N8" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="O8" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="P8" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="Q8" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+      <c r="R8" t="s">
+        <v>422</v>
+      </c>
+      <c r="S8" t="s">
+        <v>423</v>
+      </c>
+      <c r="T8" t="s">
+        <v>423</v>
+      </c>
+      <c r="U8" t="s">
+        <v>424</v>
+      </c>
+      <c r="V8" t="s">
+        <v>425</v>
+      </c>
+      <c r="W8" t="s">
+        <v>426</v>
+      </c>
+      <c r="X8" t="s">
+        <v>426</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>427</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>427</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>427</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>427</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>427</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>428</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>429</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>430</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>430</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>430</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>430</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>431</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>431</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-    </row>
-    <row r="10" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="D9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="U9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="V9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="W9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AA9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AB9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AC9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AE9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="AF9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="AG9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AH9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AI9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AJ9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AK9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AL9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AM9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AN9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AO9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AP9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="AQ9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AR9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AS9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AT9" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="AU9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AV9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AW9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AX9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AY9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="AZ9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="BA9" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="BB9" s="16" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-    </row>
-    <row r="11" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="D10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="U10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="W10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="Z10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AA10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AB10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AC10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AE10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AF10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AG10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AH10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AI10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AJ10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AK10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AL10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AM10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AN10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AO10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AP10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AQ10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AS10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AT10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AU10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AV10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AW10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AX10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AY10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AZ10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="BA10" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="BB10" s="19" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-    </row>
-    <row r="12" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="17"/>
+      <c r="AO11" s="17"/>
+      <c r="AP11" s="17"/>
+      <c r="AQ11" s="17"/>
+      <c r="AR11" s="17"/>
+      <c r="AS11" s="17"/>
+      <c r="AT11" s="17"/>
+      <c r="AU11" s="17"/>
+      <c r="AV11" s="17"/>
+      <c r="AW11" s="17"/>
+      <c r="AX11" s="17"/>
+      <c r="AY11" s="17"/>
+      <c r="AZ11" s="17"/>
+      <c r="BA11" s="17"/>
+      <c r="BB11" s="17"/>
+    </row>
+    <row r="12" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-    </row>
-    <row r="13" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="17"/>
+      <c r="AO12" s="17"/>
+      <c r="AP12" s="17"/>
+      <c r="AQ12" s="17"/>
+      <c r="AR12" s="17"/>
+      <c r="AS12" s="17"/>
+      <c r="AT12" s="17"/>
+      <c r="AU12" s="17"/>
+      <c r="AV12" s="17"/>
+      <c r="AW12" s="17"/>
+      <c r="AX12" s="17"/>
+      <c r="AY12" s="17"/>
+      <c r="AZ12" s="17"/>
+      <c r="BA12" s="17"/>
+      <c r="BB12" s="17"/>
+    </row>
+    <row r="13" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" t="s">
-        <v>420</v>
-      </c>
-      <c r="G13" t="s">
-        <v>421</v>
-      </c>
-      <c r="H13" t="s">
-        <v>422</v>
-      </c>
-      <c r="I13" t="s">
-        <v>423</v>
-      </c>
-      <c r="J13" t="s">
-        <v>424</v>
+      <c r="E13" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>493</v>
       </c>
       <c r="K13" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="L13" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="M13" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="N13" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="O13" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="P13" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="Q13" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="R13" t="s">
+        <v>443</v>
+      </c>
+      <c r="S13" t="s">
+        <v>441</v>
+      </c>
+      <c r="T13" t="s">
+        <v>442</v>
+      </c>
+      <c r="U13" t="s">
+        <v>444</v>
+      </c>
+      <c r="V13" t="s">
+        <v>445</v>
+      </c>
+      <c r="W13" t="s">
+        <v>447</v>
+      </c>
+      <c r="X13" t="s">
+        <v>446</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>448</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>449</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>450</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>451</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>452</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>453</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>472</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>487</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>475</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>477</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>479</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>481</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>483</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>484</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>485</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>486</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>455</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>456</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>457</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>458</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>459</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>462</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>463</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>465</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>467</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>468</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>469</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>470</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="14" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="24" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="22">
+        <v>3.14</v>
+      </c>
+      <c r="E14" s="22">
         <v>3.43</v>
       </c>
-      <c r="E14" s="22">
-        <v>3.14</v>
-      </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
+        <v>3.43</v>
+      </c>
+      <c r="G14" s="22">
+        <v>3.43</v>
+      </c>
+      <c r="H14" s="22">
+        <v>3.43</v>
+      </c>
+      <c r="I14" s="22">
+        <v>3.43</v>
+      </c>
+      <c r="J14" s="22">
+        <v>3.43</v>
+      </c>
+      <c r="K14" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="L14" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="M14" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="N14" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="O14" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="P14" s="17">
+        <v>1.2</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>1.2</v>
+      </c>
+      <c r="R14" s="17">
+        <v>1.2</v>
+      </c>
+      <c r="S14" s="17">
+        <v>1.2</v>
+      </c>
+      <c r="T14" s="17">
+        <v>1.2</v>
+      </c>
+      <c r="U14" s="17">
+        <v>0</v>
+      </c>
+      <c r="V14" s="17">
         <v>2</v>
       </c>
-      <c r="G14" s="21">
+      <c r="W14" s="17">
+        <v>10</v>
+      </c>
+      <c r="X14" s="17">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="17">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="17">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="17">
         <v>2</v>
       </c>
-      <c r="H14" s="21">
-        <v>1.2</v>
-      </c>
-      <c r="I14" s="21">
-        <v>1.2</v>
-      </c>
-      <c r="J14" s="21">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
+      <c r="AC14" s="17">
         <v>2</v>
       </c>
-      <c r="L14" s="21">
-        <v>10</v>
-      </c>
-      <c r="M14" s="21" t="s">
+      <c r="AD14" s="17">
+        <v>2</v>
+      </c>
+      <c r="AE14" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="N14" s="21" t="s">
-        <v>448</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="P14" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q14" s="23" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="AF14" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="AG14" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="AH14" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="AI14" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="AJ14" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="AK14" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="AL14" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="AM14" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="AN14" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="AO14" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="AP14" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="AQ14" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="AR14" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="AS14" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="AT14" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="AU14" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="AV14" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="AW14" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="AX14" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="AY14" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="AZ14" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="BA14" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="BB14" s="18" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="16">
         <v>0</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="16">
         <v>0</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-    </row>
-    <row r="16" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="17"/>
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="17"/>
+      <c r="AN15" s="17"/>
+      <c r="AO15" s="17"/>
+      <c r="AP15" s="17"/>
+      <c r="AQ15" s="17"/>
+      <c r="AR15" s="17"/>
+      <c r="AS15" s="17"/>
+      <c r="AT15" s="17"/>
+      <c r="AU15" s="17"/>
+      <c r="AV15" s="17"/>
+      <c r="AW15" s="17"/>
+      <c r="AX15" s="17"/>
+      <c r="AY15" s="17"/>
+      <c r="AZ15" s="17"/>
+      <c r="BA15" s="17"/>
+      <c r="BB15" s="17"/>
+    </row>
+    <row r="16" spans="1:54" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="16">
         <v>0</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="16">
         <v>0</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-    </row>
-    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="F16" s="16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0</v>
+      </c>
+      <c r="H16" s="16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16">
+        <v>0</v>
+      </c>
+      <c r="J16" s="16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="17"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="17"/>
+      <c r="AN16" s="17"/>
+      <c r="AO16" s="17"/>
+      <c r="AP16" s="17"/>
+      <c r="AQ16" s="17"/>
+      <c r="AR16" s="17"/>
+      <c r="AS16" s="17"/>
+      <c r="AT16" s="17"/>
+      <c r="AU16" s="17"/>
+      <c r="AV16" s="17"/>
+      <c r="AW16" s="17"/>
+      <c r="AX16" s="17"/>
+      <c r="AY16" s="17"/>
+      <c r="AZ16" s="17"/>
+      <c r="BA16" s="17"/>
+      <c r="BB16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D17" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D18" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D19" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D20" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D21" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="D22" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="21" t="s">
-        <v>448</v>
-      </c>
+      <c r="D23" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2421,1817 +3536,1817 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="A2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="A18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="8" t="s">
+      <c r="A21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="8" t="s">
+      <c r="A22" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="8" t="s">
+      <c r="A23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="8" t="s">
+      <c r="A24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="A25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="A28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="A29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="A30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="7" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="8" t="s">
+      <c r="A31" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="8" t="s">
+      <c r="A32" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="7" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="A33" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="8" t="s">
+      <c r="A35" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="7" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="8" t="s">
+      <c r="A36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="8" t="s">
+      <c r="A37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="8" t="s">
+      <c r="A38" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="8" t="s">
+      <c r="A39" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B40" s="8" t="s">
+      <c r="A40" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="8" t="s">
+      <c r="A41" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" s="8" t="s">
+      <c r="A42" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="7" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="7" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="8" t="s">
+      <c r="A44" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="8" t="s">
+      <c r="A45" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="7" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="8" t="s">
+      <c r="A46" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" s="8" t="s">
+      <c r="A47" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="7" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="8" t="s">
+      <c r="A48" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49" s="8" t="s">
+      <c r="A49" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="7" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="8" t="s">
+      <c r="A50" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51" s="8" t="s">
+      <c r="A51" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="7" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B52" s="8" t="s">
+      <c r="A52" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="7" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="8" t="s">
+      <c r="A53" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="8" t="s">
+      <c r="A54" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="7" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55" s="8" t="s">
+      <c r="A55" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="8" t="s">
+      <c r="A56" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="7" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="8" t="s">
+      <c r="A57" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="7" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="8" t="s">
+      <c r="A58" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" s="8" t="s">
+      <c r="A59" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="8" t="s">
+      <c r="A60" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="7" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B61" s="8" t="s">
+      <c r="A61" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="8" t="s">
+      <c r="A62" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" s="8" t="s">
+      <c r="A63" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="C63" s="9" t="s">
+      <c r="C63" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="8" t="s">
+      <c r="A64" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="7" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="8" t="s">
+      <c r="A65" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66" s="8" t="s">
+      <c r="A66" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="s">
+      <c r="A67" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="8" t="s">
+      <c r="A68" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="8" t="s">
+      <c r="A69" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70" s="8" t="s">
+      <c r="A70" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="8" t="s">
+      <c r="A71" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C71" s="9" t="s">
+      <c r="C71" s="7" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B72" s="8" t="s">
+      <c r="A72" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="8" t="s">
+      <c r="A73" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B74" s="8" t="s">
+      <c r="A74" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="7" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="8" t="s">
+      <c r="A75" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B76" s="8" t="s">
+      <c r="A76" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="7" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="8" t="s">
+      <c r="A77" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="7" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B78" s="8" t="s">
+      <c r="A78" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B79" s="8" t="s">
+      <c r="A79" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="7" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="8" t="s">
+      <c r="A80" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B81" s="8" t="s">
+      <c r="A81" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="7" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B82" s="8" t="s">
+      <c r="A82" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="7" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B83" s="8" t="s">
+      <c r="A83" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="C83" s="7" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B84" s="8" t="s">
+      <c r="A84" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="7" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B85" s="8" t="s">
+      <c r="A85" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="C85" s="9" t="s">
+      <c r="C85" s="7" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B86" s="8" t="s">
+      <c r="A86" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" s="7" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B87" s="8" t="s">
+      <c r="A87" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C87" s="9" t="s">
+      <c r="C87" s="7" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B88" s="8" t="s">
+      <c r="A88" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="7" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B89" s="8" t="s">
+      <c r="A89" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="7" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B90" s="8" t="s">
+      <c r="A90" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="7" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B91" s="8" t="s">
+      <c r="A91" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" s="7" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B92" s="8" t="s">
+      <c r="A92" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="7" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B93" s="8" t="s">
+      <c r="A93" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B93" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C93" s="9" t="s">
+      <c r="C93" s="7" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B94" s="8" t="s">
+      <c r="A94" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C94" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B95" s="8" t="s">
+      <c r="A95" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C95" s="7" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B96" s="8" t="s">
+      <c r="A96" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="7" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B97" s="8" t="s">
+      <c r="A97" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C97" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B98" s="8" t="s">
+      <c r="A98" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="7" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B99" s="8" t="s">
+      <c r="A99" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B99" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="C99" s="9" t="s">
+      <c r="C99" s="7" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B100" s="8" t="s">
+      <c r="A100" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="7" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B101" s="8" t="s">
+      <c r="A101" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B101" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="7" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B102" s="8" t="s">
+      <c r="A102" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="7" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B103" s="8" t="s">
+      <c r="A103" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B103" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="7" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B104" s="8" t="s">
+      <c r="A104" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B104" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C104" s="7" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B105" s="8" t="s">
+      <c r="A105" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B105" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C105" s="9" t="s">
+      <c r="C105" s="7" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B106" s="8" t="s">
+      <c r="A106" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C106" s="9" t="s">
+      <c r="C106" s="7" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B107" s="8" t="s">
+      <c r="A107" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B107" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C107" s="9" t="s">
+      <c r="C107" s="7" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B108" s="8" t="s">
+      <c r="A108" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B108" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="7" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B109" s="8" t="s">
+      <c r="A109" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B109" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="C109" s="9" t="s">
+      <c r="C109" s="7" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B110" s="8" t="s">
+      <c r="A110" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C110" s="7" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B111" s="8" t="s">
+      <c r="A111" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B111" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="7" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B112" s="8" t="s">
+      <c r="A112" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="7" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B113" s="8" t="s">
+      <c r="A113" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B113" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="C113" s="7" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B114" s="8" t="s">
+      <c r="A114" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="7" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B115" s="8" t="s">
+      <c r="A115" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B115" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C115" s="9" t="s">
+      <c r="C115" s="7" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B116" s="8" t="s">
+      <c r="A116" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B116" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C116" s="9" t="s">
+      <c r="C116" s="7" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B117" s="8" t="s">
+      <c r="A117" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B117" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="C117" s="9" t="s">
+      <c r="C117" s="7" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B118" s="8" t="s">
+      <c r="A118" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C118" s="9" t="s">
+      <c r="C118" s="7" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B119" s="8" t="s">
+      <c r="A119" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="C119" s="7" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B120" s="8" t="s">
+      <c r="A120" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C120" s="9" t="s">
+      <c r="C120" s="7" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B121" s="8" t="s">
+      <c r="A121" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B121" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C121" s="9" t="s">
+      <c r="C121" s="7" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B122" s="8" t="s">
+      <c r="A122" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B122" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C122" s="9" t="s">
+      <c r="C122" s="7" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B123" s="8" t="s">
+      <c r="A123" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B123" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="C123" s="9" t="s">
+      <c r="C123" s="7" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B124" s="8" t="s">
+      <c r="A124" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B124" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C124" s="7" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B125" s="8" t="s">
+      <c r="A125" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B125" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="7" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B126" s="8" t="s">
+      <c r="A126" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B126" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" s="7" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B127" s="8" t="s">
+      <c r="A127" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B127" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="C127" s="7" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B128" s="8" t="s">
+      <c r="A128" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B128" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="7" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B129" s="8" t="s">
+      <c r="A129" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B129" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="C129" s="7" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B130" s="8" t="s">
+      <c r="A130" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C130" s="9" t="s">
+      <c r="C130" s="7" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B131" s="8" t="s">
+      <c r="A131" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B131" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="7" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B132" s="8" t="s">
+      <c r="A132" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B132" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="7" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B133" s="8" t="s">
+      <c r="A133" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B133" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" s="7" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B134" s="8" t="s">
+      <c r="A134" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B134" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="7" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B135" s="8" t="s">
+      <c r="A135" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B135" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" s="7" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B136" s="8" t="s">
+      <c r="A136" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B136" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="7" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B137" s="8" t="s">
+      <c r="A137" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B137" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="C137" s="9" t="s">
+      <c r="C137" s="7" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B138" s="8" t="s">
+      <c r="A138" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B138" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="7" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B139" s="8" t="s">
+      <c r="A139" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B139" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="7" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B140" s="8" t="s">
+      <c r="A140" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B140" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="C140" s="9" t="s">
+      <c r="C140" s="7" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B141" s="8" t="s">
+      <c r="A141" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B141" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="7" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B142" s="8" t="s">
+      <c r="A142" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="7" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B143" s="8" t="s">
+      <c r="A143" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B143" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="7" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B144" s="8" t="s">
+      <c r="A144" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B144" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="7" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A145" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B145" s="8" t="s">
+      <c r="A145" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B145" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="7" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B146" s="8" t="s">
+      <c r="A146" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B146" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="7" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B147" s="8" t="s">
+      <c r="A147" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B147" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="7" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B148" s="8" t="s">
+      <c r="A148" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B148" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="7" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B149" s="8" t="s">
+      <c r="A149" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B149" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="7" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B150" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C150" s="9" t="s">
+      <c r="C150" s="7" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
+      <c r="A151" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B151" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" s="7" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+      <c r="A152" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C152" s="9" t="s">
+      <c r="C152" s="7" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
+      <c r="A153" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C153" s="9" t="s">
+      <c r="C153" s="7" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B154" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C154" s="9" t="s">
+      <c r="C154" s="7" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
+      <c r="A155" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B155" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C155" s="9" t="s">
+      <c r="C155" s="7" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B156" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="C156" s="9" t="s">
+      <c r="C156" s="7" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="7" t="s">
+      <c r="A157" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B157" s="8" t="s">
+      <c r="B157" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C157" s="7" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
+      <c r="A158" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B158" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="C158" s="9" t="s">
+      <c r="C158" s="7" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="7" t="s">
+      <c r="A159" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B159" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C159" s="7" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="B160" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="C160" s="9" t="s">
+      <c r="C160" s="7" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
+      <c r="A161" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B161" s="8" t="s">
+      <c r="B161" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="C161" s="9" t="s">
+      <c r="C161" s="7" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A162" s="7" t="s">
+      <c r="A162" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="C162" s="9" t="s">
+      <c r="C162" s="7" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="7" t="s">
+      <c r="A163" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B163" s="8" t="s">
+      <c r="B163" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="C163" s="9" t="s">
+      <c r="C163" s="7" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="7" t="s">
+      <c r="A164" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B164" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="9" t="s">
+      <c r="C164" s="7" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="7" t="s">
+      <c r="A165" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="C165" s="9" t="s">
+      <c r="C165" s="7" t="s">
         <v>391</v>
       </c>
     </row>
@@ -4252,531 +5367,531 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="11" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="11" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="11" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="11" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="11" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="135" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="11" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="11" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="11" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="11" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="11" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="11" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="11" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="11" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="11" t="s">
         <v>399</v>
       </c>
     </row>

--- a/Veenkampen/misc/BADM-Instrument_Ops/VK-BADM-Instrument_Ops.xlsx
+++ b/Veenkampen/misc/BADM-Instrument_Ops/VK-BADM-Instrument_Ops.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\ESG\DOW_MAQ\MAQ_Archive\Veenkampen_archive\FLUXNET\Veenkampen\misc\BADM-Instrument_Ops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F5DF23-D4FE-4049-986A-573891CBE370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9886C8-98ED-40D5-8773-7F73A5CF177D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-6525" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54495" yWindow="-6525" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrument_Ops" sheetId="1" r:id="rId1"/>
@@ -2111,7 +2111,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="16">
-        <v>20250521</v>
+        <v>20250911</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
